--- a/individual_Tests/tabela syscalls.xlsx
+++ b/individual_Tests/tabela syscalls.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jorge\Desktop\Masters\Tests\initial_tests\individual_Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{188A8A5D-9C62-4777-9E8B-006A45155247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A27B137-E61A-4546-85D7-A8DED09B34C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6675" yWindow="6000" windowWidth="18345" windowHeight="9330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Syscall Test Matrix" sheetId="1" r:id="rId1"/>
@@ -859,7 +859,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -960,7 +960,7 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1506,7 +1506,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -1532,7 +1532,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="20" t="s">
         <v>63</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -1584,7 +1584,7 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>72</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -1599,8 +1599,8 @@
       <c r="F16" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="6" t="s">
-        <v>13</v>
+      <c r="G16" s="9" t="s">
+        <v>71</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>14</v>
@@ -2364,7 +2364,7 @@
       <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="21" t="s">
         <v>201</v>
       </c>
       <c r="C46" s="17" t="s">
